--- a/report-006-manual-006.xlsx
+++ b/report-006-manual-006.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>{"baseline_commit": "5f0b902c77c8156df4c9ea32d4512430732ce742", "fix_commit": "168f271c99ae580287b35dd6a63141d39f185f17", "fix_passed": true, "red_failed": true, "test_commit": "c9914d637674cb4986dc9bd98930f65086062ed5"}</t>
+          <t>{"pre_fix": {"commit": "c9914d637674cb4986dc9bd98930f65086062ed5", "result": "red", "trajectory_url": "未生成"}}</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
